--- a/ecv/extraccion_ecv_2019/ecv_2019_wide.xlsx
+++ b/ecv/extraccion_ecv_2019/ecv_2019_wide.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -402,62 +402,77 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>dep_economica_total</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>IMCV_urbano</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>estrato_urbano</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>calidad_vivienda_urbano</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_pub_urbano</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_suspendidos_urbano</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>tasa_desempleo_urbano</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dep_economica_urbano</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>IMCV_rural</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>estrato_rural</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>calidad_vivienda_rural</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_pub_rural</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_suspendidos_rural</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>tasa_desempleo_rural</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dep_economica_rural</t>
         </is>
       </c>
     </row>
@@ -494,40 +509,49 @@
         <v>5.31032682309779</v>
       </c>
       <c r="J2">
+        <v>53.5771439090818</v>
+      </c>
+      <c r="K2">
         <v>27.8726446808511</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.00466964285714286</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.0165830357142857</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>1.5031</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>6.62640775390801</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
+        <v>53.9325842696629</v>
+      </c>
+      <c r="R2">
         <v>23.5834462962963</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>0</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>0</v>
       </c>
-      <c r="S2">
+      <c r="U2">
         <v>0.00479922480620155</v>
       </c>
-      <c r="T2">
+      <c r="V2">
         <v>1.41140542635659</v>
       </c>
-      <c r="U2">
+      <c r="W2">
         <v>4.97001686379457</v>
+      </c>
+      <c r="X2">
+        <v>53.4891165172856</v>
       </c>
     </row>
     <row r="3">
@@ -563,40 +587,49 @@
         <v>10.950486996252</v>
       </c>
       <c r="J3">
+        <v>62.7087902611178</v>
+      </c>
+      <c r="K3">
         <v>30.6802640552995</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.365313100436681</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.542279475982533</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>1.51400655021834</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>1.49398471615721</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>17.4182315226868</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
+        <v>62.8559859809361</v>
+      </c>
+      <c r="R3">
         <v>25.4021983333333</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>0</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>0.033741935483871</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>0.2951</v>
       </c>
-      <c r="T3">
+      <c r="V3">
         <v>1.49187741935484</v>
       </c>
-      <c r="U3">
+      <c r="W3">
         <v>5.63288161579896</v>
+      </c>
+      <c r="X3">
+        <v>62.6010947446109</v>
       </c>
     </row>
     <row r="4">
@@ -632,40 +665,49 @@
         <v>17.103301700844</v>
       </c>
       <c r="J4">
+        <v>59.161566864021</v>
+      </c>
+      <c r="K4">
         <v>30.4605964285714</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.437899176954732</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.6716744855967079</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>1.60367366255144</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>1.47446625514403</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>18.951313289501</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>59.1120289106866</v>
+      </c>
+      <c r="R4">
         <v>25.7891012048193</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>0</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>0.113695652173913</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>0.0874815217391304</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>1.5031</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>3.24873219496549</v>
+      </c>
+      <c r="X4">
+        <v>59.5151901217997</v>
       </c>
     </row>
     <row r="5">
@@ -701,40 +743,49 @@
         <v>4.62242315083032</v>
       </c>
       <c r="J5">
+        <v>55.9455884456027</v>
+      </c>
+      <c r="K5">
         <v>29.21275</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.262525</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.455821212121212</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>1.30245757575758</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>1.5031</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>7.20846317552129</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
+        <v>56.0906695163145</v>
+      </c>
+      <c r="R5">
         <v>25.7147387596899</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>0</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>0.0898282442748092</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>0.446922900763359</v>
       </c>
-      <c r="T5">
+      <c r="V5">
         <v>1.5031</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>2.2956058764469</v>
+      </c>
+      <c r="X5">
+        <v>55.8014245941354</v>
       </c>
     </row>
     <row r="6">
@@ -770,40 +821,49 @@
         <v>7.77359774908556</v>
       </c>
       <c r="J6">
+        <v>72.055555684075</v>
+      </c>
+      <c r="K6">
         <v>26.8526815028902</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.0471955056179775</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>0.166574719101124</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>1.33178033707865</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>1.46015730337079</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>15.0639797838598</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
+        <v>72.3014064882981</v>
+      </c>
+      <c r="R6">
         <v>24.1178448</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>0</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <v>0.0663507462686567</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>0.201220895522388</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <v>1.4719447761194</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>3.58133168174533</v>
+      </c>
+      <c r="X6">
+        <v>71.939631078815</v>
       </c>
     </row>
     <row r="7">
@@ -839,40 +899,49 @@
         <v>3.71818017867817</v>
       </c>
       <c r="J7">
+        <v>65.70854469242499</v>
+      </c>
+      <c r="K7">
         <v>30.0693297709924</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.0443704225352113</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.208627464788732</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>1.49867816901408</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>1.4835</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>7.09567495722417</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
+        <v>67.14197962756739</v>
+      </c>
+      <c r="R7">
         <v>27.4867137254902</v>
       </c>
-      <c r="Q7">
+      <c r="S7">
         <v>0</v>
       </c>
-      <c r="R7">
+      <c r="T7">
         <v>0.0450862068965517</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>0.313693965517241</v>
       </c>
-      <c r="T7">
+      <c r="V7">
         <v>1.5031</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>0.594386062555783</v>
+      </c>
+      <c r="X7">
+        <v>64.5190374837413</v>
       </c>
     </row>
     <row r="8">
@@ -908,40 +977,49 @@
         <v>8.784263762119551</v>
       </c>
       <c r="J8">
+        <v>53.2660284785182</v>
+      </c>
+      <c r="K8">
         <v>25.1082846153846</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.0256121951219512</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.0031890243902439</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.0151</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>1.27411707317073</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>13.2943951191613</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
+        <v>54.6802786783473</v>
+      </c>
+      <c r="R8">
         <v>24.5994909090909</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
         <v>1.37146216216216</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>5.80219431911463</v>
+      </c>
+      <c r="X8">
+        <v>52.4280820055468</v>
       </c>
     </row>
     <row r="9">
@@ -977,40 +1055,49 @@
         <v>13.5126264448898</v>
       </c>
       <c r="J9">
+        <v>60.1473172265935</v>
+      </c>
+      <c r="K9">
         <v>32.8598856031128</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.460473404255319</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.686174113475177</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>1.72498546099291</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>1.47595886524823</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>13.9832226586282</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
+        <v>60.0410230910277</v>
+      </c>
+      <c r="R9">
         <v>28.5416358695652</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>0.0329874345549738</v>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>0.174956544502618</v>
       </c>
-      <c r="S9">
+      <c r="U9">
         <v>0.430298952879581</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>1.49945706806283</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>10.1598750987803</v>
+      </c>
+      <c r="X9">
+        <v>60.8451538839761</v>
       </c>
     </row>
     <row r="10">
@@ -1046,40 +1133,49 @@
         <v>5.74565601614934</v>
       </c>
       <c r="J10">
+        <v>59.708936638232</v>
+      </c>
+      <c r="K10">
         <v>28.5575196969697</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.324329370629371</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>0.560102097902098</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>1.60898811188811</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>1.47390559440559</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>5.041374444919</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
+        <v>59.8773674887587</v>
+      </c>
+      <c r="R10">
         <v>26.9010573099415</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>0.0948396648044693</v>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>0.251915642458101</v>
       </c>
-      <c r="S10">
+      <c r="U10">
         <v>0.814372625698324</v>
       </c>
-      <c r="T10">
+      <c r="V10">
         <v>1.5031</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>8.385625648277109</v>
+      </c>
+      <c r="X10">
+        <v>59.1228403265615</v>
       </c>
     </row>
     <row r="11">
@@ -1115,40 +1211,49 @@
         <v>8.492792278514271</v>
       </c>
       <c r="J11">
+        <v>59.1788298785792</v>
+      </c>
+      <c r="K11">
         <v>29.4562631205674</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.13218041958042</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.345288111888112</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>1.58688391608392</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>1.4885027972028</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>10.0808379529227</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
+        <v>59.8835463339172</v>
+      </c>
+      <c r="R11">
         <v>25.9615112149533</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>0.009460360360360361</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>0.132041441441441</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>0.273886486486486</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>1.49683153153153</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>7.92480253404869</v>
+      </c>
+      <c r="X11">
+        <v>58.9479799569122</v>
       </c>
     </row>
     <row r="12">
@@ -1184,40 +1289,49 @@
         <v>18.9748031563965</v>
       </c>
       <c r="J12">
+        <v>60.6067145645753</v>
+      </c>
+      <c r="K12">
         <v>27.9451671755725</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.3305</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.488271223021583</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>1.1997309352518</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>1.47310143884892</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>24.0126859342644</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
+        <v>60.2197154986953</v>
+      </c>
+      <c r="R12">
         <v>26.0511056338028</v>
       </c>
-      <c r="Q12">
+      <c r="S12">
         <v>0.075497385620915</v>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>0.227365359477124</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>0.743224836601307</v>
       </c>
-      <c r="T12">
+      <c r="V12">
         <v>1.4849091503268</v>
       </c>
-      <c r="U12">
+      <c r="W12">
         <v>15.7557583129323</v>
+      </c>
+      <c r="X12">
+        <v>60.8657130391623</v>
       </c>
     </row>
   </sheetData>
